--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="104">
   <si>
     <t>Size</t>
   </si>
@@ -271,6 +271,63 @@
   </si>
   <si>
     <t>DIN3055 Steel Wire Rope, 6x7+FC, Reel packing</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/Anchor_bolt_with_hook_HG.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/Anchor_wedge_MAN.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/DIN763_chain_LONG_link.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/DIN766_chain_SHORT_link.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/DIN_3055_braided_rope.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/DIN_3055_rope_without_braid.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screw_for_parquet.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_Fluegel_zinc.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_GKD_3.5_AND_3.9_AND_4.2.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_GKM.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_Press_Washer_SHARP.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_Press_washer_DRILL.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_UNIVERSAL_yellow_full_thread.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_UNIVERSAL_yellow_part_thread.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_countersunk_structural_self_tapping.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_for_ROOF_zinc_n1_AND_n3.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_for_metal_DRILL_PHOSPHAT_PMS.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_for_metal_SHARP_PHOSPHAT_PM.png</t>
+  </si>
+  <si>
+    <t>resources/images/metalware/screws_for_metal_in_TAPE.png</t>
   </si>
 </sst>
 </file>
@@ -766,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>78</v>
@@ -801,7 +858,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>79</v>
@@ -850,7 +907,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>81</v>
@@ -885,7 +942,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>82</v>
@@ -920,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>83</v>
@@ -955,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="J9" s="13" t="s">
         <v>84</v>
@@ -990,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>78</v>
@@ -1025,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>79</v>
@@ -1075,7 +1132,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="J13" s="13" t="s">
         <v>81</v>
@@ -1125,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>83</v>
@@ -1160,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="J16" s="13" t="s">
         <v>84</v>
@@ -1210,7 +1267,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="J18" s="13" t="s">
         <v>79</v>
@@ -1245,7 +1302,7 @@
         <v>4</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>80</v>
@@ -1295,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>82</v>
@@ -1330,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>83</v>
@@ -1380,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J24" s="13" t="s">
         <v>80</v>
@@ -1940,7 +1997,7 @@
         <v>4</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>46</v>
@@ -1970,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>46</v>
@@ -2000,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>46</v>
@@ -2030,7 +2087,7 @@
         <v>4</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>46</v>
@@ -2060,7 +2117,7 @@
         <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>46</v>
@@ -2090,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>46</v>

--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="105">
   <si>
     <t>Size</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>resources/images/metalware/screws_for_metal_in_TAPE.png</t>
+  </si>
+  <si>
+    <t>Csk Head Pozi Drive Chipboard Screw, Partial thread</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="112.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -805,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -840,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -889,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -924,7 +927,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
@@ -959,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
@@ -994,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
@@ -1029,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
@@ -1064,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>7</v>
@@ -1453,7 +1456,9 @@
       <c r="A25" s="4">
         <v>17</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
@@ -1480,7 +1485,9 @@
       <c r="A26" s="4">
         <v>18</v>
       </c>
-      <c r="B26" s="4"/>
+      <c r="B26" s="13" t="s">
+        <v>82</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>24</v>
       </c>
@@ -1507,7 +1514,9 @@
       <c r="A27" s="4">
         <v>19</v>
       </c>
-      <c r="B27" s="4"/>
+      <c r="B27" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="C27" s="3" t="s">
         <v>24</v>
       </c>
@@ -1534,7 +1543,9 @@
       <c r="A28" s="4">
         <v>20</v>
       </c>
-      <c r="B28" s="4"/>
+      <c r="B28" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="C28" s="3" t="s">
         <v>24</v>
       </c>
@@ -1561,7 +1572,9 @@
       <c r="A29" s="4">
         <v>21</v>
       </c>
-      <c r="B29" s="4"/>
+      <c r="B29" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>24</v>
       </c>
@@ -1588,7 +1601,9 @@
       <c r="A30" s="4">
         <v>22</v>
       </c>
-      <c r="B30" s="4"/>
+      <c r="B30" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C30" s="3" t="s">
         <v>24</v>
       </c>
@@ -1615,7 +1630,9 @@
       <c r="A31" s="4">
         <v>23</v>
       </c>
-      <c r="B31" s="4"/>
+      <c r="B31" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C31" s="3" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1659,9 @@
       <c r="A32" s="4">
         <v>24</v>
       </c>
-      <c r="B32" s="4"/>
+      <c r="B32" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="C32" s="3" t="s">
         <v>24</v>
       </c>
@@ -1669,7 +1688,9 @@
       <c r="A33" s="4">
         <v>25</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C33" s="3" t="s">
         <v>24</v>
       </c>
@@ -1708,7 +1729,9 @@
       <c r="A35" s="4">
         <v>26</v>
       </c>
-      <c r="B35" s="4"/>
+      <c r="B35" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>35</v>
       </c>
@@ -1735,7 +1758,9 @@
       <c r="A36" s="4">
         <v>27</v>
       </c>
-      <c r="B36" s="4"/>
+      <c r="B36" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>35</v>
       </c>
@@ -1762,7 +1787,9 @@
       <c r="A37" s="4">
         <v>28</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C37" s="3" t="s">
         <v>35</v>
       </c>
@@ -1789,7 +1816,9 @@
       <c r="A38" s="4">
         <v>29</v>
       </c>
-      <c r="B38" s="4"/>
+      <c r="B38" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C38" s="3" t="s">
         <v>35</v>
       </c>
@@ -1828,7 +1857,9 @@
       <c r="A40" s="4">
         <v>30</v>
       </c>
-      <c r="B40" s="4"/>
+      <c r="B40" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C40" s="3" t="s">
         <v>40</v>
       </c>
@@ -1856,7 +1887,9 @@
       <c r="A41" s="4">
         <v>31</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C41" s="3" t="s">
         <v>40</v>
       </c>
@@ -1884,7 +1917,9 @@
       <c r="A42" s="4">
         <v>32</v>
       </c>
-      <c r="B42" s="4"/>
+      <c r="B42" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C42" s="3" t="s">
         <v>40</v>
       </c>
@@ -1912,7 +1947,9 @@
       <c r="A43" s="4">
         <v>33</v>
       </c>
-      <c r="B43" s="4"/>
+      <c r="B43" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C43" s="3" t="s">
         <v>40</v>
       </c>
@@ -1940,7 +1977,9 @@
       <c r="A44" s="4">
         <v>34</v>
       </c>
-      <c r="B44" s="4"/>
+      <c r="B44" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>40</v>
       </c>
@@ -1980,7 +2019,9 @@
       <c r="A46" s="4">
         <v>35</v>
       </c>
-      <c r="B46" s="4"/>
+      <c r="B46" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>46</v>
       </c>
@@ -2010,7 +2051,9 @@
       <c r="A47" s="4">
         <v>36</v>
       </c>
-      <c r="B47" s="4"/>
+      <c r="B47" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>46</v>
       </c>
@@ -2040,7 +2083,9 @@
       <c r="A48" s="4">
         <v>37</v>
       </c>
-      <c r="B48" s="4"/>
+      <c r="B48" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>46</v>
       </c>
@@ -2070,7 +2115,9 @@
       <c r="A49" s="4">
         <v>38</v>
       </c>
-      <c r="B49" s="4"/>
+      <c r="B49" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>46</v>
       </c>
@@ -2100,7 +2147,9 @@
       <c r="A50" s="4">
         <v>39</v>
       </c>
-      <c r="B50" s="4"/>
+      <c r="B50" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>46</v>
       </c>
@@ -2130,7 +2179,9 @@
       <c r="A51" s="4">
         <v>40</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>46</v>
       </c>

--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="106">
   <si>
     <t>Size</t>
   </si>
@@ -273,64 +273,67 @@
     <t>DIN3055 Steel Wire Rope, 6x7+FC, Reel packing</t>
   </si>
   <si>
-    <t>resources/images/metalware/Anchor_bolt_with_hook_HG.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/Anchor_wedge_MAN.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/DIN763_chain_LONG_link.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/DIN766_chain_SHORT_link.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/DIN_3055_braided_rope.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/DIN_3055_rope_without_braid.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screw_for_parquet.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_Fluegel_zinc.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_GKD_3.5_AND_3.9_AND_4.2.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_GKM.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_Press_Washer_SHARP.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_Press_washer_DRILL.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_UNIVERSAL_yellow_full_thread.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_UNIVERSAL_yellow_part_thread.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_countersunk_structural_self_tapping.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_for_ROOF_zinc_n1_AND_n3.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_for_metal_DRILL_PHOSPHAT_PMS.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_for_metal_SHARP_PHOSPHAT_PM.png</t>
-  </si>
-  <si>
-    <t>resources/images/metalware/screws_for_metal_in_TAPE.png</t>
-  </si>
-  <si>
     <t>Csk Head Pozi Drive Chipboard Screw, Partial thread</t>
+  </si>
+  <si>
+    <t>Anchor_bolt_with_hook_HG.png</t>
+  </si>
+  <si>
+    <t>Anchor_wedge_MAN.png</t>
+  </si>
+  <si>
+    <t>DIN763_chain_LONG_link.png</t>
+  </si>
+  <si>
+    <t>DIN766_chain_SHORT_link.png</t>
+  </si>
+  <si>
+    <t>DIN_3055_braided_rope.png</t>
+  </si>
+  <si>
+    <t>DIN_3055_rope_without_braid.png</t>
+  </si>
+  <si>
+    <t>screw_for_parquet.png</t>
+  </si>
+  <si>
+    <t>screws_Fluegel_zinc.png</t>
+  </si>
+  <si>
+    <t>screws_GKD_3.5_AND_3.9_AND_4.2.png</t>
+  </si>
+  <si>
+    <t>screws_GKM.png</t>
+  </si>
+  <si>
+    <t>screws_Press_Washer_SHARP.png</t>
+  </si>
+  <si>
+    <t>screws_Press_washer_DRILL.png</t>
+  </si>
+  <si>
+    <t>screws_UNIVERSAL_yellow_full_thread.png</t>
+  </si>
+  <si>
+    <t>screws_UNIVERSAL_yellow_part_thread.png</t>
+  </si>
+  <si>
+    <t>screws_countersunk_structural_self_tapping.png</t>
+  </si>
+  <si>
+    <t>screws_for_ROOF_zinc_n1_AND_n3.png</t>
+  </si>
+  <si>
+    <t>screws_for_metal_DRILL_PHOSPHAT_PMS.png</t>
+  </si>
+  <si>
+    <t>screws_for_metal_SHARP_PHOSPHAT_PM.png</t>
+  </si>
+  <si>
+    <t>screws_for_metal_in_TAPE.png</t>
+  </si>
+  <si>
+    <t>Alter_image_name</t>
   </si>
 </sst>
 </file>
@@ -791,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>76</v>
@@ -808,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -826,7 +829,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>78</v>
@@ -843,7 +846,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -861,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>79</v>
@@ -892,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -910,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>81</v>
@@ -927,7 +930,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
@@ -945,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>82</v>
@@ -962,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
@@ -980,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>83</v>
@@ -997,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
@@ -1015,7 +1018,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9" s="13" t="s">
         <v>84</v>
@@ -1032,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
@@ -1050,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>78</v>
@@ -1067,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>7</v>
@@ -1085,7 +1088,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>79</v>
@@ -1135,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J13" s="13" t="s">
         <v>81</v>
@@ -1185,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>83</v>
@@ -1220,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J16" s="13" t="s">
         <v>84</v>
@@ -1270,7 +1273,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J18" s="13" t="s">
         <v>79</v>
@@ -1305,7 +1308,7 @@
         <v>4</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>80</v>
@@ -1355,7 +1358,7 @@
         <v>4</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>82</v>
@@ -1390,7 +1393,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>83</v>
@@ -1440,7 +1443,7 @@
         <v>4</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J24" s="13" t="s">
         <v>80</v>
@@ -2038,7 +2041,7 @@
         <v>4</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>46</v>
@@ -2070,7 +2073,7 @@
         <v>4</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>46</v>
@@ -2102,7 +2105,7 @@
         <v>4</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>46</v>
@@ -2134,7 +2137,7 @@
         <v>4</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>46</v>
@@ -2166,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>46</v>
@@ -2198,7 +2201,7 @@
         <v>4</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>46</v>
